--- a/artfynd/A 48341-2025 artfynd.xlsx
+++ b/artfynd/A 48341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87024852</v>
+        <v>72773103</v>
       </c>
       <c r="B2" t="n">
-        <v>108183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,17 +703,33 @@
           <t>(L.) Huds.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogstorp, 100 m NV om, Srm</t>
+          <t>Tullgarn, Skogstorp 50 m N, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646734.6438993633</v>
+        <v>646819</v>
       </c>
       <c r="R2" t="n">
-        <v>6539673.906987473</v>
+        <v>6539635</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,26 +770,1289 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Trädgård</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskog längs liten stig</t>
+          <t>Vägkant med trädgårdsliknande struktur, vid liten klippa med basisk markpåverkan</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87024852</v>
+      </c>
+      <c r="B3" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogstorp, 100 m NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>646735</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6539674</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrskog längs liten stig</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Hans Rydberg, Rolf Wahlström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94926566</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>G:a Stockholmsvägen, 220-320 m N trevägskorset, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>646809</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539635</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Varav 290 blommande: 150 blommande ex. på västra sidan utmed hela sträckan; 140 blommande ex. på östra sidan från 10-40 meter.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>I dikeskant vid mindre skogsväg och i intilliggande ängsmark.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95222532</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stigen mot Skräddartorpskärret., Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>646764</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Utmed stigen till Skräddartorpskärret.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97234732</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogstorp, N om, Södertälje, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>646829</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539705</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Längs med vägen. Minst 200.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110794201</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skäddartorpskärret O om, vid grusvägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>646810</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539661</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grusvägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Lennart Karlén, Stefan Clason</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126756004</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111377</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stor bockrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pimpinella major</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nykrogen, Tullgarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>646811</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6539660</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tillsammans med kirskål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grusvägkant, örtrik</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>79603662</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tullgarn, Skogstorp 50 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>646819</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6539635</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>På västvänd, översilad basisk klippa.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129522996</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91502</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tullgarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>646904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6539806</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På mycket grov stock av ask.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95213045</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tullgarns naturvårdsområde, 225 m N Nykrogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>646844</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6539822</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>14 blommande. Växer intill och uppe på ett mindre stenblock.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blockig, mossig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97330286</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tullgarns NV-område, 225 m N Nykrogen (*knärot* /stjälk/), Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>646844</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539823</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>AB-Söd-0277</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tullgarns naturvårdsområde, 225 m N Nykrogen, Obskoord: 6540316/1600605/5 m (). 14 blommande. Växer intill och uppe på ett mindre stenblock.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blockig, mossig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>94714126</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tullgarns naturreservat, parkeringen till Skräddartorpskärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>646829</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539702</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48341-2025 artfynd.xlsx
+++ b/artfynd/A 48341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72773103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87024852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94926566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95222532</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97234732</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110794201</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126756004</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79603662</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522996</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95213045</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330286</t>
         </is>
       </c>
     </row>
@@ -2053,8 +2113,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94714126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>